--- a/Data_clean/MCAS/Estados_US/Edos_USA_2021/ALASKA_2021.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2021/ALASKA_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C3">
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Guachochi</t>
@@ -522,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C12">
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -581,7 +631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -651,7 +721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -667,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C22">
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -724,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C26">
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -757,7 +852,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C28">
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -781,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C30">
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -807,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C32">
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -851,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -864,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ixtlahuacán de los Membrillos</t>
+          <t>Ixtlahuacán De Los Membrillos</t>
         </is>
       </c>
       <c r="C36">
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -916,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C40">
@@ -929,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -942,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -955,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C43">
@@ -968,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -981,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -994,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1007,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Valle de Guadalupe</t>
+          <t>Valle De Guadalupe</t>
         </is>
       </c>
       <c r="C47">
@@ -1020,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -1033,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1064,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Charo</t>
@@ -1077,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Churintzio</t>
@@ -1090,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Ecuandureo</t>
@@ -1103,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1116,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -1129,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1142,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1173,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -1186,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1206,7 +1446,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bahía de Banderas</t>
+          <t>Bahía De Banderas</t>
         </is>
       </c>
       <c r="C61">
@@ -1217,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1230,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1261,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -1274,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1294,7 +1554,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C67">
@@ -1305,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C68">
@@ -1318,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -1331,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C70">
@@ -1344,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1375,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1388,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -1401,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -1414,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -1427,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -1440,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1471,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1502,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nacozari de García</t>
+          <t>Nacozari De García</t>
         </is>
       </c>
       <c r="C82">
@@ -1515,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1535,7 +1860,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C84">
@@ -1546,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C85">
@@ -1559,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -1572,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1603,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Luis Moya</t>
@@ -1616,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Monte Escobedo</t>
@@ -1629,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -1642,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1665,41 +2025,6 @@
       </c>
       <c r="D93">
         <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
